--- a/Map1.xlsx
+++ b/Map1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\administratie\git\BossRegion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0924AA2-188A-4B82-BE22-CE22A10771DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9FD12E35-C34E-43FD-9BBB-4620722C5493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16410" yWindow="19560" windowWidth="16290" windowHeight="8400" xr2:uid="{7A496937-2003-426A-974A-D7B5FE0EB809}"/>
   </bookViews>
@@ -26,7 +26,7 @@
     <sheet name="Morytania" sheetId="4" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Map1'!$A$1:$D$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Map1'!$A$1:$E$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="122">
   <si>
     <t>boss</t>
   </si>
@@ -322,6 +322,102 @@
   </si>
   <si>
     <t>chunk_13_34, chunk_13_35, chunk_13_36, chunk_13_37, chunk_14_34, chunk_14_35, chunk_14_36, chunk_14_37, chunk_15_34, chunk_15_35, chunk_15_36, chunk_15_37, chunk_15_38, chunk_16_34, chunk_16_35, chunk_16_36, chunk_16_37, chunk_16_38, chunk_17_33, chunk_17_34, chunk_17_35, chunk_17_36, chunk_17_37, chunk_17_38, chunk_18_33, chunk_18_34, chunk_18_35, chunk_18_36, chunk_18_37, chunk_18_38, chunk_18_39, chunk_19_33, chunk_19_34, chunk_19_35, chunk_19_36, chunk_19_37, chunk_19_38, chunk_20_31, chunk_20_32, chunk_20_33, chunk_20_34, chunk_20_35, chunk_20_36, chunk_20_37, chunk_21_33, chunk_21_34, chunk_21_35, chunk_21_36, chunk_21_37, chunk_22_33, chunk_22_34, chunk_22_35, chunk_22_36, chunk_22_37, chunk_23_33, chunk_23_34, chunk_23_36, chunk_23_40</t>
+  </si>
+  <si>
+    <t>Giant_Mole</t>
+  </si>
+  <si>
+    <t>Royal_titans</t>
+  </si>
+  <si>
+    <t>Commander_Zilyana</t>
+  </si>
+  <si>
+    <t>General_Graardor</t>
+  </si>
+  <si>
+    <t>Kril_Tsutsaroth</t>
+  </si>
+  <si>
+    <t>Kree_arra</t>
+  </si>
+  <si>
+    <t>The_Whisperer</t>
+  </si>
+  <si>
+    <t>Kalphite_Queen</t>
+  </si>
+  <si>
+    <t>Tombs_of_Amascut</t>
+  </si>
+  <si>
+    <t>The_Leviathan</t>
+  </si>
+  <si>
+    <t>Dagannoth_Rex</t>
+  </si>
+  <si>
+    <t>Phantom_Muspah</t>
+  </si>
+  <si>
+    <t>Duke_Sucellus</t>
+  </si>
+  <si>
+    <t>TzTok-Jad</t>
+  </si>
+  <si>
+    <t>TzKal-Zuk</t>
+  </si>
+  <si>
+    <t>Chambers_of_Xeric</t>
+  </si>
+  <si>
+    <t>Deranged_archaeologist</t>
+  </si>
+  <si>
+    <t>Theatre_of_Blood</t>
+  </si>
+  <si>
+    <t>The_Nightmare</t>
+  </si>
+  <si>
+    <t>Corrupted_Hunllef</t>
+  </si>
+  <si>
+    <t>Crystalline_Hunllef</t>
+  </si>
+  <si>
+    <t>The_Hueycoatl</t>
+  </si>
+  <si>
+    <t>Moons_of_peril</t>
+  </si>
+  <si>
+    <t>Doom_of_Mokhaiotl</t>
+  </si>
+  <si>
+    <t>Fortis_Colosseum</t>
+  </si>
+  <si>
+    <t>Crazy_archaeologist</t>
+  </si>
+  <si>
+    <t>Chaos_Fanatic</t>
+  </si>
+  <si>
+    <t>Chaos_Elemental</t>
+  </si>
+  <si>
+    <t>Vetion</t>
+  </si>
+  <si>
+    <t>King_Black_Dragon</t>
+  </si>
+  <si>
+    <t>Corporeal_Beast</t>
+  </si>
+  <si>
+    <t>boss_image_reference</t>
   </si>
 </sst>
 </file>
@@ -708,732 +804,886 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FE193D8-2E71-44B3-9679-2580500B6E3B}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
       <c r="B2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
       <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>54</v>
       </c>
       <c r="B4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>56</v>
       </c>
       <c r="B5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>57</v>
       </c>
       <c r="B6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>6</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>58</v>
       </c>
       <c r="B7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>60</v>
       </c>
       <c r="B8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>6</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
       <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>8</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>3</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>39</v>
       </c>
       <c r="B10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>5</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>59</v>
       </c>
       <c r="B11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" t="s">
         <v>8</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>6</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>62</v>
       </c>
       <c r="B12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" t="s">
         <v>8</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>6</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
       <c r="B13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" t="s">
         <v>14</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>4</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
       <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
         <v>14</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>5</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>52</v>
       </c>
       <c r="B15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" t="s">
         <v>14</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>6</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>61</v>
       </c>
       <c r="B16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" t="s">
         <v>14</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>6</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>37</v>
       </c>
       <c r="B17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>5</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>63</v>
       </c>
       <c r="B18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>7</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
       <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
         <v>10</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>3</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>38</v>
       </c>
       <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
         <v>10</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>5</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>43</v>
       </c>
       <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
         <v>10</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>5</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>45</v>
       </c>
       <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
         <v>10</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>5</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
       <c r="B23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" t="s">
         <v>10</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>6</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>67</v>
       </c>
       <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" t="s">
         <v>10</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>7</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>18</v>
       </c>
       <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>3</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>19</v>
       </c>
       <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>3</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>20</v>
       </c>
       <c r="B27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" t="s">
         <v>9</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>3</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>21</v>
       </c>
       <c r="B28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" t="s">
         <v>9</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>3</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
       <c r="B29" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" t="s">
         <v>9</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>5</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>24</v>
       </c>
       <c r="B30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" t="s">
         <v>11</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>4</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>51</v>
       </c>
       <c r="B31" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" t="s">
         <v>11</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>6</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>65</v>
       </c>
       <c r="B32" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" t="s">
         <v>11</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>7</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
       <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" t="s">
         <v>16</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>5</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>47</v>
       </c>
       <c r="B34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" t="s">
         <v>16</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>5</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>48</v>
       </c>
       <c r="B35" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" t="s">
         <v>16</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>6</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>49</v>
       </c>
       <c r="B36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" t="s">
         <v>16</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>6</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>30</v>
       </c>
       <c r="B37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" t="s">
         <v>15</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>5</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>41</v>
       </c>
       <c r="B38" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" t="s">
         <v>15</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>5</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>42</v>
       </c>
       <c r="B39" t="s">
+        <v>112</v>
+      </c>
+      <c r="C39" t="s">
         <v>15</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>5</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>50</v>
       </c>
       <c r="B40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" t="s">
         <v>15</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>6</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>64</v>
       </c>
       <c r="B41" t="s">
+        <v>113</v>
+      </c>
+      <c r="C41" t="s">
         <v>15</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>7</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>66</v>
       </c>
       <c r="B42" t="s">
+        <v>114</v>
+      </c>
+      <c r="C42" t="s">
         <v>15</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>7</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>25</v>
       </c>
       <c r="B43" t="s">
+        <v>115</v>
+      </c>
+      <c r="C43" t="s">
         <v>12</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>4</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>29</v>
       </c>
       <c r="B44" t="s">
+        <v>116</v>
+      </c>
+      <c r="C44" t="s">
         <v>12</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>4</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>31</v>
       </c>
       <c r="B45" t="s">
+        <v>117</v>
+      </c>
+      <c r="C45" t="s">
         <v>12</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>5</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>32</v>
       </c>
       <c r="B46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" t="s">
         <v>12</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>5</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>33</v>
       </c>
       <c r="B47" t="s">
+        <v>118</v>
+      </c>
+      <c r="C47" t="s">
         <v>12</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>5</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>40</v>
       </c>
       <c r="B48" t="s">
+        <v>119</v>
+      </c>
+      <c r="C48" t="s">
         <v>12</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>5</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>44</v>
       </c>
       <c r="B49" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" t="s">
         <v>12</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>5</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>46</v>
       </c>
       <c r="B50" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" t="s">
         <v>12</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>5</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>55</v>
       </c>
       <c r="B51" t="s">
+        <v>120</v>
+      </c>
+      <c r="C51" t="s">
         <v>12</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>6</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D51" xr:uid="{4FE193D8-2E71-44B3-9679-2580500B6E3B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D51">
-      <sortCondition ref="B1:B51"/>
+  <autoFilter ref="A1:E51" xr:uid="{4FE193D8-2E71-44B3-9679-2580500B6E3B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E51">
+      <sortCondition ref="C1:C51"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Map1.xlsx
+++ b/Map1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\administratie\git\BossRegion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9FD12E35-C34E-43FD-9BBB-4620722C5493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B5665337-16D0-417D-9C93-A57318F7DD11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16410" yWindow="19560" windowWidth="16290" windowHeight="8400" xr2:uid="{7A496937-2003-426A-974A-D7B5FE0EB809}"/>
+    <workbookView xWindow="-16410" yWindow="20535" windowWidth="16290" windowHeight="7425" xr2:uid="{7A496937-2003-426A-974A-D7B5FE0EB809}"/>
   </bookViews>
   <sheets>
     <sheet name="Map1" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="135">
   <si>
     <t>boss</t>
   </si>
@@ -273,9 +273,6 @@
     <t>chunk_11_1, chunk_11_2, chunk_11_3, chunk_11_4, chunk_11_5, chunk_12_1, chunk_12_2, chunk_12_3, chunk_12_4, chunk_12_5, chunk_12_6, chunk_12_7, chunk_12_8, chunk_13_1, chunk_13_2, chunk_13_3, chunk_13_4, chunk_13_5, chunk_13_6, chunk_13_7, chunk_13_8, chunk_13_9, chunk_13_10, chunk_14_2, chunk_14_3, chunk_14_4, chunk_14_5, chunk_14_6, chunk_14_7, chunk_14_8, chunk_14_9, chunk_14_10, chunk_15_2, chunk_15_3, chunk_15_4, chunk_15_5, chunk_15_6, chunk_15_7, chunk_15_8, chunk_15_9, chunk_15_10, chunk_15_11, chunk_15_12, chunk_16_2, chunk_16_3, chunk_16_4, chunk_16_5, chunk_16_6, chunk_16_7, chunk_16_8, chunk_16_9, chunk_16_10, chunk_16_11, chunk_16_12, chunk_16_13, chunk_17_3, chunk_17_4, chunk_17_5, chunk_17_6, chunk_17_7, chunk_17_8, chunk_17_9, chunk_17_10, chunk_17_11, chunk_17_12, chunk_18_3, chunk_18_4, chunk_18_5, chunk_18_6, chunk_18_7, chunk_18_8, chunk_18_9, chunk_18_10, chunk_18_11, chunk_19_4, chunk_19_5, chunk_19_6, chunk_19_7, chunk_19_8, chunk_19_9, chunk_19_10, chunk_19_11, chunk_20_5, chunk_20_6</t>
   </si>
   <si>
-    <t>chunk_4_20, chunk_4_21, chunk_4_22, chunk_4_23, chunk_4_24, chunk_4_25, chunk_5_20, chunk_5_21, chunk_5_23, chunk_5_26, chunk_6_20, chunk_6_23, chunk_6_25, chunk_6_26, chunk_7_23, chunk_7_24, chunk_7_25, chunk_7_26, chunk_7_27, chunk_8_23, chunk_8_24, chunk_8_25, chunk_8_26, chunk_8_27</t>
-  </si>
-  <si>
     <t>chunk_10_32, chunk_10_33, chunk_10_34, chunk_10_35, chunk_10_36, chunk_10_37, chunk_11_32, chunk_11_33, chunk_11_34, chunk_11_35, chunk_11_36, chunk_12_32, chunk_12_33, chunk_12_34, chunk_12_35, chunk_12_36, chunk_13_32, chunk_13_33, chunk_13_34, chunk_14_32, chunk_14_33, chunk_14_34, chunk_15_32, chunk_15_33, chunk_15_34, chunk_16_32, chunk_17_33</t>
   </si>
   <si>
@@ -285,9 +282,6 @@
     <t>chunk_10_32, chunk_10_33, chunk_10_34, chunk_10_35, chunk_10_36, chunk_10_37, chunk_11_32, chunk_11_33, chunk_11_34, chunk_11_35, chunk_11_36, chunk_12_32, chunk_12_33, chunk_12_34, chunk_12_35, chunk_12_36, chunk_13_32, chunk_13_33, chunk_13_34, chunk_14_32, chunk_14_33, chunk_14_34, chunk_15_32, chunk_15_33, chunk_15_34, chunk_16_32, chunk_17_35</t>
   </si>
   <si>
-    <t>chunk_9_27, chunk_9_28, chunk_9_29, chunk_9_30, chunk_9_31, chunk_10_27, chunk_10_28, chunk_10_29, chunk_10_30, chunk_10_31, chunk_11_28, chunk_11_29, chunk_11_30, chunk_11_31, chunk_12_28, chunk_12_29, chunk_12_30, chunk_12_31, chunk_13_28, chunk_13_29, chunk_13_30, chunk_13_31, chunk_14_28, chunk_14_30, chunk_14_31, chunk_15_30, chunk_15_31, chunk_16_30</t>
-  </si>
-  <si>
     <t>chunk_3_30, chunk_3_31, chunk_3_32, chunk_3_33, chunk_3_34, chunk_3_35, chunk_3_36, chunk_4_30, chunk_4_31, chunk_4_32, chunk_4_33, chunk_4_34, chunk_4_35, chunk_4_36, chunk_5_30, chunk_5_31, chunk_5_32, chunk_5_33, chunk_5_34, chunk_5_35, chunk_5_36, chunk_6_30, chunk_6_31, chunk_6_32, chunk_6_33, chunk_6_34, chunk_6_35, chunk_6_36, chunk_7_30, chunk_7_31, chunk_7_32, chunk_7_33, chunk_7_34, chunk_7_35, chunk_7_36, chunk_8_30, chunk_8_31, chunk_8_32, chunk_8_33, chunk_8_34, chunk_8_35, chunk_8_36, chunk_9_30, chunk_9_31, chunk_9_32, chunk_9_33, chunk_9_34, chunk_9_35, chunk_9_36</t>
   </si>
   <si>
@@ -300,21 +294,6 @@
     <t>chunk_8_37, chunk_9_37, chunk_9_38, chunk_9_39, chunk_9_40, chunk_9_41, chunk_10_37, chunk_10_38, chunk_10_39, chunk_10_40, chunk_10_41, chunk_11_37, chunk_11_38, chunk_11_39, chunk_11_40, chunk_11_41, chunk_11_42, chunk_12_37, chunk_12_38, chunk_12_39, chunk_12_40, chunk_12_41, chunk_12_42, chunk_13_37, chunk_13_38, chunk_13_39, chunk_13_40, chunk_13_41, chunk_13_42, chunk_14_37, chunk_14_38, chunk_14_39, chunk_14_40, chunk_14_41, chunk_14_42, chunk_15_37, chunk_15_38, chunk_15_39, chunk_15_40, chunk_15_41, chunk_15_42</t>
   </si>
   <si>
-    <t>chunk_9_27, chunk_9_28, chunk_9_29, chunk_9_30, chunk_9_31, chunk_10_27, chunk_10_28, chunk_10_29, chunk_10_30, chunk_10_31, chunk_11_28, chunk_11_29, chunk_11_30, chunk_11_31, chunk_12_28, chunk_12_29, chunk_12_30, chunk_12_31, chunk_13_28, chunk_13_29, chunk_13_30, chunk_13_31, chunk_14_28, chunk_14_30, chunk_14_31, chunk_15_30, chunk_15_31, chunk_16_31</t>
-  </si>
-  <si>
-    <t>chunk_9_27, chunk_9_28, chunk_9_29, chunk_9_30, chunk_9_31, chunk_10_27, chunk_10_28, chunk_10_29, chunk_10_30, chunk_10_31, chunk_11_28, chunk_11_29, chunk_11_30, chunk_11_31, chunk_12_28, chunk_12_29, chunk_12_30, chunk_12_31, chunk_13_28, chunk_13_29, chunk_13_30, chunk_13_31, chunk_14_28, chunk_14_30, chunk_14_31, chunk_15_30, chunk_15_31, chunk_16_32</t>
-  </si>
-  <si>
-    <t>chunk_9_27, chunk_9_28, chunk_9_29, chunk_9_30, chunk_9_31, chunk_10_27, chunk_10_28, chunk_10_29, chunk_10_30, chunk_10_31, chunk_11_28, chunk_11_29, chunk_11_30, chunk_11_31, chunk_12_28, chunk_12_29, chunk_12_30, chunk_12_31, chunk_13_28, chunk_13_29, chunk_13_30, chunk_13_31, chunk_14_28, chunk_14_30, chunk_14_31, chunk_15_30, chunk_15_31, chunk_16_33</t>
-  </si>
-  <si>
-    <t>chunk_9_27, chunk_9_28, chunk_9_29, chunk_9_30, chunk_9_31, chunk_10_27, chunk_10_28, chunk_10_29, chunk_10_30, chunk_10_31, chunk_11_28, chunk_11_29, chunk_11_30, chunk_11_31, chunk_12_28, chunk_12_29, chunk_12_30, chunk_12_31, chunk_13_28, chunk_13_29, chunk_13_30, chunk_13_31, chunk_14_28, chunk_14_30, chunk_14_31, chunk_15_30, chunk_15_31, chunk_16_34</t>
-  </si>
-  <si>
-    <t>chunk_9_27, chunk_9_28, chunk_9_29, chunk_9_30, chunk_9_31, chunk_10_27, chunk_10_28, chunk_10_29, chunk_10_30, chunk_10_31, chunk_11_28, chunk_11_29, chunk_11_30, chunk_11_31, chunk_12_28, chunk_12_29, chunk_12_30, chunk_12_31, chunk_13_28, chunk_13_29, chunk_13_30, chunk_13_31, chunk_14_28, chunk_14_30, chunk_14_31, chunk_15_30, chunk_15_31, chunk_16_35</t>
-  </si>
-  <si>
     <t>chunk_13_34, chunk_13_35, chunk_13_36, chunk_13_37, chunk_14_34, chunk_14_35, chunk_14_36, chunk_14_37, chunk_15_34, chunk_15_35, chunk_15_36, chunk_15_37, chunk_15_38, chunk_16_34, chunk_16_35, chunk_16_36, chunk_16_37, chunk_16_38, chunk_17_33, chunk_17_34, chunk_17_35, chunk_17_36, chunk_17_37, chunk_17_38, chunk_18_33, chunk_18_34, chunk_18_35, chunk_18_36, chunk_18_37, chunk_18_38, chunk_18_39, chunk_19_33, chunk_19_34, chunk_19_35, chunk_19_36, chunk_19_37, chunk_19_38, chunk_20_31, chunk_20_32, chunk_20_33, chunk_20_34, chunk_20_35, chunk_20_36, chunk_20_37, chunk_21_33, chunk_21_34, chunk_21_35, chunk_21_36, chunk_21_37, chunk_22_33, chunk_22_34, chunk_22_35, chunk_22_36, chunk_22_37, chunk_23_33, chunk_23_34, chunk_23_36, chunk_23_38</t>
   </si>
   <si>
@@ -418,6 +397,66 @@
   </si>
   <si>
     <t>boss_image_reference</t>
+  </si>
+  <si>
+    <t>chunk_6_28</t>
+  </si>
+  <si>
+    <t>chunk_7_28</t>
+  </si>
+  <si>
+    <t>chunk_8_28</t>
+  </si>
+  <si>
+    <t>chunk_6_29</t>
+  </si>
+  <si>
+    <t>chunk_7_29</t>
+  </si>
+  <si>
+    <t>chunk_8_29</t>
+  </si>
+  <si>
+    <t>chunk_6_28, chunk_6_29, chunk_7_28, chunk_7_29, chunk_9_27, chunk_9_28, chunk_9_29, chunk_9_30, chunk_9_31, chunk_10_27, chunk_10_28, chunk_10_29, chunk_10_30, chunk_10_31, chunk_11_28, chunk_11_29, chunk_11_30, chunk_11_31, chunk_12_28, chunk_12_29, chunk_12_30, chunk_12_31, chunk_13_28, chunk_13_29, chunk_13_30, chunk_13_31, chunk_14_28, chunk_14_29, chunk_14_30, chunk_14_31, chunk_15_30, chunk_15_31, chunk_16_30</t>
+  </si>
+  <si>
+    <t>chunk_3_29</t>
+  </si>
+  <si>
+    <t>chunk_4_29</t>
+  </si>
+  <si>
+    <t>chunk_4_28</t>
+  </si>
+  <si>
+    <t>chunk_3_28</t>
+  </si>
+  <si>
+    <t>chunk_2_28</t>
+  </si>
+  <si>
+    <t>chunk_5_29</t>
+  </si>
+  <si>
+    <t>chunk_5_28</t>
+  </si>
+  <si>
+    <t>chunk_4_27</t>
+  </si>
+  <si>
+    <t>chunk_5_27</t>
+  </si>
+  <si>
+    <t>chunk_6_27</t>
+  </si>
+  <si>
+    <t>chunk_3_27</t>
+  </si>
+  <si>
+    <t>chunk_4_26</t>
+  </si>
+  <si>
+    <t>chunk_2_28, chunk_2_29, chunk_3_27, chunk_3_28, chunk_3_29, chunk_4_20, chunk_4_21, chunk_4_22, chunk_4_23, chunk_4_24, chunk_4_25, chunk_4_26, chunk_4_27, chunk_5_20, chunk_5_21, chunk_5_23, chunk_5_26, chunk_5_27, chunk_5_28, chunk_5_29, chunk_6_20, chunk_6_23, chunk_6_25, chunk_6_26, chunk_6_27, chunk_7_23, chunk_7_24, chunk_7_25, chunk_7_26, chunk_7_27, chunk_8_23, chunk_8_24, chunk_8_25, chunk_8_26, chunk_8_27</t>
   </si>
 </sst>
 </file>
@@ -818,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -835,7 +874,7 @@
         <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -844,7 +883,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -852,7 +891,7 @@
         <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -861,7 +900,7 @@
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -869,7 +908,7 @@
         <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -878,7 +917,7 @@
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -886,7 +925,7 @@
         <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -895,7 +934,7 @@
         <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -903,7 +942,7 @@
         <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -912,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -920,7 +959,7 @@
         <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -929,7 +968,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -937,7 +976,7 @@
         <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
@@ -946,7 +985,7 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -963,7 +1002,7 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -971,7 +1010,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -980,7 +1019,7 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -988,7 +1027,7 @@
         <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
@@ -997,7 +1036,7 @@
         <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1005,7 +1044,7 @@
         <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
@@ -1014,7 +1053,7 @@
         <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1022,7 +1061,7 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
@@ -1031,7 +1070,7 @@
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1048,7 +1087,7 @@
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1056,7 +1095,7 @@
         <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
@@ -1065,7 +1104,7 @@
         <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1073,7 +1112,7 @@
         <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
@@ -1082,7 +1121,7 @@
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1090,7 +1129,7 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
         <v>17</v>
@@ -1107,7 +1146,7 @@
         <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
         <v>17</v>
@@ -1133,7 +1172,7 @@
         <v>3</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1150,7 +1189,7 @@
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1167,7 +1206,7 @@
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1184,7 +1223,7 @@
         <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1192,7 +1231,7 @@
         <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
@@ -1201,7 +1240,7 @@
         <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1218,7 +1257,7 @@
         <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1252,7 +1291,7 @@
         <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1269,7 +1308,7 @@
         <v>3</v>
       </c>
       <c r="E27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1286,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1294,7 +1333,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
@@ -1303,7 +1342,7 @@
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1320,7 +1359,7 @@
         <v>4</v>
       </c>
       <c r="E30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1328,7 +1367,7 @@
         <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -1337,7 +1376,7 @@
         <v>6</v>
       </c>
       <c r="E31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1345,7 +1384,7 @@
         <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -1354,7 +1393,7 @@
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1396,7 +1435,7 @@
         <v>48</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
         <v>16</v>
@@ -1413,7 +1452,7 @@
         <v>49</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
         <v>16</v>
@@ -1447,7 +1486,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C38" t="s">
         <v>15</v>
@@ -1464,7 +1503,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
         <v>15</v>
@@ -1498,7 +1537,7 @@
         <v>64</v>
       </c>
       <c r="B41" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C41" t="s">
         <v>15</v>
@@ -1515,7 +1554,7 @@
         <v>66</v>
       </c>
       <c r="B42" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C42" t="s">
         <v>15</v>
@@ -1532,7 +1571,7 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
@@ -1541,7 +1580,7 @@
         <v>4</v>
       </c>
       <c r="E43" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1549,7 +1588,7 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
@@ -1558,7 +1597,7 @@
         <v>4</v>
       </c>
       <c r="E44" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -1566,7 +1605,7 @@
         <v>31</v>
       </c>
       <c r="B45" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C45" t="s">
         <v>12</v>
@@ -1575,7 +1614,7 @@
         <v>5</v>
       </c>
       <c r="E45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1592,7 +1631,7 @@
         <v>5</v>
       </c>
       <c r="E46" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -1600,7 +1639,7 @@
         <v>33</v>
       </c>
       <c r="B47" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>12</v>
@@ -1609,7 +1648,7 @@
         <v>5</v>
       </c>
       <c r="E47" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1617,7 +1656,7 @@
         <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
         <v>12</v>
@@ -1626,7 +1665,7 @@
         <v>5</v>
       </c>
       <c r="E48" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -1643,7 +1682,7 @@
         <v>5</v>
       </c>
       <c r="E49" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -1660,7 +1699,7 @@
         <v>5</v>
       </c>
       <c r="E50" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1668,7 +1707,7 @@
         <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C51" t="s">
         <v>12</v>
@@ -1677,7 +1716,7 @@
         <v>6</v>
       </c>
       <c r="E51" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -3526,7 +3565,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B393ECD9-BBDD-42D7-8296-05F81F4152A5}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -3536,7 +3575,7 @@
     <col min="15" max="18" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B1">
         <v>20</v>
       </c>
@@ -3568,128 +3607,184 @@
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="K1">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
+        <f>A3-1</f>
+        <v>2</v>
+      </c>
+      <c r="J2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <f>A4-1</f>
+        <v>3</v>
+      </c>
+      <c r="I3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>4</v>
       </c>
-      <c r="B2" t="str">
-        <f>"chunk_"&amp;$A2&amp;"_"&amp;B$1</f>
+      <c r="B4" t="str">
+        <f>"chunk_"&amp;$A4&amp;"_"&amp;B$1</f>
         <v>chunk_4_20</v>
       </c>
-      <c r="C2" t="str">
-        <f t="shared" ref="C2:N11" si="2">"chunk_"&amp;$A2&amp;"_"&amp;C$1</f>
+      <c r="C4" t="str">
+        <f t="shared" ref="C4:N13" si="2">"chunk_"&amp;$A4&amp;"_"&amp;C$1</f>
         <v>chunk_4_21</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D4" t="str">
         <f t="shared" si="2"/>
         <v>chunk_4_22</v>
       </c>
-      <c r="E2" t="str">
+      <c r="E4" t="str">
         <f t="shared" si="2"/>
         <v>chunk_4_23</v>
       </c>
-      <c r="F2" t="str">
+      <c r="F4" t="str">
         <f t="shared" si="2"/>
         <v>chunk_4_24</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G4" t="str">
         <f t="shared" si="2"/>
         <v>chunk_4_25</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <f>A2+1</f>
-        <v>5</v>
-      </c>
-      <c r="B3" t="str">
-        <f>"chunk_"&amp;$A3&amp;"_"&amp;B$1</f>
-        <v>chunk_5_20</v>
-      </c>
-      <c r="C3" t="str">
-        <f t="shared" si="2"/>
-        <v>chunk_5_21</v>
-      </c>
-      <c r="E3" t="str">
-        <f t="shared" si="2"/>
-        <v>chunk_5_23</v>
-      </c>
-      <c r="H3" t="str">
-        <f t="shared" si="2"/>
-        <v>chunk_5_26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <f>A3+1</f>
-        <v>6</v>
-      </c>
-      <c r="B4" t="str">
-        <f t="shared" ref="B4:E10" si="3">"chunk_"&amp;$A4&amp;"_"&amp;B$1</f>
-        <v>chunk_6_20</v>
-      </c>
-      <c r="E4" t="str">
-        <f t="shared" si="2"/>
-        <v>chunk_6_23</v>
-      </c>
-      <c r="G4" t="str">
-        <f t="shared" si="2"/>
-        <v>chunk_6_25</v>
-      </c>
-      <c r="H4" t="str">
-        <f t="shared" si="2"/>
-        <v>chunk_6_26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I4" t="s">
+        <v>129</v>
+      </c>
+      <c r="J4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>A4+1</f>
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="B5" t="str">
+        <f>"chunk_"&amp;$A5&amp;"_"&amp;B$1</f>
+        <v>chunk_5_20</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_5_21</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="2"/>
-        <v>chunk_7_23</v>
-      </c>
-      <c r="F5" t="str">
-        <f t="shared" si="2"/>
-        <v>chunk_7_24</v>
-      </c>
-      <c r="G5" t="str">
-        <f t="shared" si="2"/>
-        <v>chunk_7_25</v>
+        <v>chunk_5_23</v>
       </c>
       <c r="H5" t="str">
         <f t="shared" si="2"/>
-        <v>chunk_7_26</v>
-      </c>
-      <c r="I5" t="str">
-        <f t="shared" si="2"/>
-        <v>chunk_7_27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>chunk_5_26</v>
+      </c>
+      <c r="I5" t="s">
+        <v>130</v>
+      </c>
+      <c r="J5" t="s">
+        <v>128</v>
+      </c>
+      <c r="K5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>A5+1</f>
+        <v>6</v>
+      </c>
+      <c r="B6" t="str">
+        <f t="shared" ref="B6:E12" si="3">"chunk_"&amp;$A6&amp;"_"&amp;B$1</f>
+        <v>chunk_6_20</v>
+      </c>
+      <c r="E6" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_6_23</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_6_25</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_6_26</v>
+      </c>
+      <c r="I6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <f>A6+1</f>
+        <v>7</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_7_23</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_7_24</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_7_25</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_7_26</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_7_27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <f>A7+1</f>
         <v>8</v>
       </c>
-      <c r="E6" t="str">
-        <f>"chunk_"&amp;$A6&amp;"_"&amp;E$1</f>
+      <c r="E8" t="str">
+        <f>"chunk_"&amp;$A8&amp;"_"&amp;E$1</f>
         <v>chunk_8_23</v>
       </c>
-      <c r="F6" t="str">
+      <c r="F8" t="str">
         <f t="shared" si="2"/>
         <v>chunk_8_24</v>
       </c>
-      <c r="G6" t="str">
+      <c r="G8" t="str">
         <f t="shared" si="2"/>
         <v>chunk_8_25</v>
       </c>
-      <c r="H6" t="str">
+      <c r="H8" t="str">
         <f t="shared" si="2"/>
         <v>chunk_8_26</v>
       </c>
-      <c r="I6" t="str">
+      <c r="I8" t="str">
         <f t="shared" si="2"/>
         <v>chunk_8_27</v>
       </c>
@@ -3701,7 +3796,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA22B8F4-4B39-4F99-99B4-46F0780D9B0D}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -3720,7 +3815,7 @@
         <v>28</v>
       </c>
       <c r="D1">
-        <f t="shared" ref="D1:R1" si="0">C1+1</f>
+        <f t="shared" ref="D1:F1" si="0">C1+1</f>
         <v>29</v>
       </c>
       <c r="E1">
@@ -3734,152 +3829,188 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>9</v>
-      </c>
-      <c r="B2" t="str">
-        <f>"chunk_"&amp;$A2&amp;"_"&amp;B$1</f>
-        <v>chunk_9_27</v>
-      </c>
-      <c r="C2" t="str">
-        <f t="shared" ref="C2:N11" si="1">"chunk_"&amp;$A2&amp;"_"&amp;C$1</f>
-        <v>chunk_9_28</v>
-      </c>
-      <c r="D2" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_9_29</v>
-      </c>
-      <c r="E2" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_9_30</v>
-      </c>
-      <c r="F2" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_9_31</v>
+        <f t="shared" ref="A2:A3" si="1">A3-1</f>
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
-        <f>A2+1</f>
-        <v>10</v>
-      </c>
-      <c r="B3" t="str">
-        <f>"chunk_"&amp;$A3&amp;"_"&amp;B$1</f>
-        <v>chunk_10_27</v>
-      </c>
-      <c r="C3" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_10_28</v>
-      </c>
-      <c r="D3" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_10_29</v>
-      </c>
-      <c r="E3" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_10_30</v>
-      </c>
-      <c r="F3" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_10_31</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
-        <f>A3+1</f>
-        <v>11</v>
-      </c>
-      <c r="C4" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_11_28</v>
-      </c>
-      <c r="D4" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_11_29</v>
-      </c>
-      <c r="E4" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_11_30</v>
-      </c>
-      <c r="F4" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_11_31</v>
+        <f>A5-1</f>
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
-        <f>A4+1</f>
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="B5" t="str">
+        <f>"chunk_"&amp;$A5&amp;"_"&amp;B$1</f>
+        <v>chunk_9_27</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" ref="C5:F11" si="2">"chunk_"&amp;$A5&amp;"_"&amp;C$1</f>
+        <v>chunk_9_28</v>
       </c>
       <c r="D5" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_12_29</v>
+        <f t="shared" si="2"/>
+        <v>chunk_9_29</v>
       </c>
       <c r="E5" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_12_30</v>
+        <f t="shared" si="2"/>
+        <v>chunk_9_30</v>
       </c>
       <c r="F5" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_12_31</v>
+        <f t="shared" si="2"/>
+        <v>chunk_9_31</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>A5+1</f>
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="B6" t="str">
+        <f>"chunk_"&amp;$A6&amp;"_"&amp;B$1</f>
+        <v>chunk_10_27</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_10_28</v>
       </c>
       <c r="D6" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_13_29</v>
+        <f t="shared" si="2"/>
+        <v>chunk_10_29</v>
       </c>
       <c r="E6" t="str">
-        <f>"chunk_"&amp;$A6&amp;"_"&amp;E$1</f>
-        <v>chunk_13_30</v>
+        <f t="shared" si="2"/>
+        <v>chunk_10_30</v>
       </c>
       <c r="F6" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_13_31</v>
+        <f t="shared" si="2"/>
+        <v>chunk_10_31</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
-        <f t="shared" ref="A7:A12" si="2">A6+1</f>
-        <v>14</v>
+        <f>A6+1</f>
+        <v>11</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_11_28</v>
       </c>
       <c r="D7" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_14_29</v>
+        <f t="shared" si="2"/>
+        <v>chunk_11_29</v>
       </c>
       <c r="E7" t="str">
-        <f t="shared" ref="E7:E9" si="3">"chunk_"&amp;$A7&amp;"_"&amp;E$1</f>
-        <v>chunk_14_30</v>
+        <f t="shared" si="2"/>
+        <v>chunk_11_30</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_14_31</v>
+        <f t="shared" si="2"/>
+        <v>chunk_11_31</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
-        <f t="shared" si="2"/>
-        <v>15</v>
+        <f>A7+1</f>
+        <v>12</v>
+      </c>
+      <c r="D8" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_12_29</v>
       </c>
       <c r="E8" t="str">
-        <f t="shared" si="3"/>
-        <v>chunk_15_30</v>
+        <f t="shared" si="2"/>
+        <v>chunk_12_30</v>
       </c>
       <c r="F8" t="str">
-        <f t="shared" si="1"/>
-        <v>chunk_15_31</v>
+        <f t="shared" si="2"/>
+        <v>chunk_12_31</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
-        <f t="shared" si="2"/>
+        <f>A8+1</f>
+        <v>13</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_13_29</v>
+      </c>
+      <c r="E9" t="str">
+        <f>"chunk_"&amp;$A9&amp;"_"&amp;E$1</f>
+        <v>chunk_13_30</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_13_31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <f t="shared" ref="A10:A12" si="3">A9+1</f>
+        <v>14</v>
+      </c>
+      <c r="D10" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_14_29</v>
+      </c>
+      <c r="E10" t="str">
+        <f t="shared" ref="E10:E12" si="4">"chunk_"&amp;$A10&amp;"_"&amp;E$1</f>
+        <v>chunk_14_30</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_14_31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="E11" t="str">
+        <f t="shared" si="4"/>
+        <v>chunk_15_30</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="2"/>
+        <v>chunk_15_31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="E9" t="str">
-        <f t="shared" si="3"/>
+      <c r="E12" t="str">
+        <f t="shared" si="4"/>
         <v>chunk_16_30</v>
       </c>
     </row>
